--- a/venues.xlsx
+++ b/venues.xlsx
@@ -1804,7 +1804,7 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>เวอร์ชันใน Claude: ไอคอนเมฆ (Backup &amp; display) → Venue list → Update from Excel แล้วเลือกไฟล์นี้</t>
+          <t>อัปเดตได้ทาง GitHub เท่านั้น ในแอปไม่มีปุ่มอัปโหลดไฟล์นี้ คนอื่นจึงแก้รายชื่อไม่ได้ (เวอร์ชันใน Claude ใช้รายชื่อที่ติดมากับแอป)</t>
         </is>
       </c>
     </row>
